--- a/output_boron/boron_Intermediate_greenop_2019.xlsx
+++ b/output_boron/boron_Intermediate_greenop_2019.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="295">
   <si>
     <t>NA</t>
   </si>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1029/2018PA003420</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_greenop_2019.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_greenop_2019_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Pälike, Frazier, and Zachos (2006; and references therein)</t>
+    <t xml:space="preserve">Pälike, Frazier, and Zachos (2006; and references therein); added age uncertainties based on power fit on LR04 uncertainties</t>
   </si>
   <si>
     <t xml:space="preserve">G. praebulloides</t>
@@ -1457,10 +1457,64 @@
     <t xml:space="preserve">ODP 926_B_50_4_88_90</t>
   </si>
   <si>
+    <t xml:space="preserve">ODP 926_B_50_6_10_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_50_5_121_124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_50_6_56_59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_51_1_12_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_51_2_109_111.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_51_3_0_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_51_3_121.5_124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_51_4_64_69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_51_6_120_122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_51_6_130_134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_52_2_57.5_60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_52_3_90_95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_52_4_95_98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_52_4_138_140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_52_5_72_74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_52_6_101_103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_53_1_10_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 926_B_53_2_39.5_41.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 872_C_13_4_20_22</t>
   </si>
   <si>
-    <t xml:space="preserve">Sosdian et al. 2018 updated to GTS2012</t>
+    <t xml:space="preserve">Sosdian et al. 2018 updated to GTS2012; added age uncertainties based on power fit on LR04 uncertainties</t>
   </si>
   <si>
     <t xml:space="preserve">T. trilobus</t>
@@ -1480,7 +1534,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1540,12 +1594,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1659,7 +1707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1741,7 +1789,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2348,7 +2395,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2366,8 +2413,8 @@
       <c r="H5" t="n">
         <v>22.022</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.10888670868436</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2425,7 +2472,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2443,8 +2490,8 @@
       <c r="H6" t="n">
         <v>22.161</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.109538280090109</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2502,7 +2549,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2520,8 +2567,8 @@
       <c r="H7" t="n">
         <v>22.442</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.110854840570871</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2579,7 +2626,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2597,8 +2644,8 @@
       <c r="H8" t="n">
         <v>22.51</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.111173310124869</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2656,7 +2703,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2674,8 +2721,8 @@
       <c r="H9" t="n">
         <v>22.521</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.111224822572034</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -2733,7 +2780,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2751,8 +2798,8 @@
       <c r="H10" t="n">
         <v>22.58</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.11150109438131</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -2810,7 +2857,7 @@
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2828,8 +2875,8 @@
       <c r="H11" t="n">
         <v>22.589</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.111543234249233</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -2887,7 +2934,7 @@
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -2905,8 +2952,8 @@
       <c r="H12" t="n">
         <v>22.661</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.111880321914377</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -2964,7 +3011,7 @@
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -2982,8 +3029,8 @@
       <c r="H13" t="n">
         <v>22.673</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.111936497793571</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3041,7 +3088,7 @@
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3059,8 +3106,8 @@
       <c r="H14" t="n">
         <v>22.696</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.11204416392466</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3118,7 +3165,7 @@
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3136,8 +3183,8 @@
       <c r="H15" t="n">
         <v>22.728</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.112193950880636</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3195,7 +3242,7 @@
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3213,8 +3260,8 @@
       <c r="H16" t="n">
         <v>22.736</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.112231395912142</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3272,7 +3319,7 @@
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3290,8 +3337,8 @@
       <c r="H17" t="n">
         <v>22.81</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.112577730132185</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3349,7 +3396,7 @@
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3367,8 +3414,8 @@
       <c r="H18" t="n">
         <v>22.815</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.112601128991835</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -3426,7 +3473,7 @@
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3444,8 +3491,8 @@
       <c r="H19" t="n">
         <v>22.82</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.112624527585858</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -3503,7 +3550,7 @@
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3521,8 +3568,8 @@
       <c r="H20" t="n">
         <v>22.872</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.112867857232344</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -3580,7 +3627,7 @@
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3598,8 +3645,8 @@
       <c r="H21" t="n">
         <v>22.895</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.112975474662584</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -3657,7 +3704,7 @@
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3675,8 +3722,8 @@
       <c r="H22" t="n">
         <v>22.939</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.113181335886873</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -3734,7 +3781,7 @@
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3752,8 +3799,8 @@
       <c r="H23" t="n">
         <v>22.968</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.113317005963073</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -3811,7 +3858,7 @@
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -3829,8 +3876,8 @@
       <c r="H24" t="n">
         <v>23.008</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.113504122545227</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -3888,7 +3935,7 @@
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -3906,8 +3953,8 @@
       <c r="H25" t="n">
         <v>23.023</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.113574286917701</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -3965,7 +4012,7 @@
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -3975,16 +4022,16 @@
         <v>244</v>
       </c>
       <c r="F26" t="n">
-        <v>10.1</v>
+        <v>3.71</v>
       </c>
       <c r="G26" t="n">
-        <v>162.87</v>
+        <v>-42.9</v>
       </c>
       <c r="H26" t="n">
-        <v>21.16732075</v>
-      </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+        <v>23.075</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.113817505086237</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -3993,13 +4040,13 @@
         <v>#N/A</v>
       </c>
       <c r="L26" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="M26" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="N26" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="O26" t="e">
         <v>#N/A</v>
@@ -4008,19 +4055,19 @@
         <v>248</v>
       </c>
       <c r="Q26" t="n">
-        <v>16.6553386622114</v>
+        <v>16.8794369670009</v>
       </c>
       <c r="R26" t="n">
-        <v>0.248765002131439</v>
+        <v>0.239799640141505</v>
       </c>
       <c r="S26" t="n">
-        <v>4.4524375655714</v>
+        <v>3.73613244565767</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
       </c>
       <c r="U26" s="9" t="n">
-        <v>29.92866</v>
+        <v>28.0587793156331</v>
       </c>
       <c r="V26" t="n">
         <v>3</v>
@@ -4037,12 +4084,12 @@
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4052,16 +4099,16 @@
         <v>244</v>
       </c>
       <c r="F27" t="n">
-        <v>10.1</v>
+        <v>3.71</v>
       </c>
       <c r="G27" t="n">
-        <v>162.87</v>
+        <v>-42.9</v>
       </c>
       <c r="H27" t="n">
-        <v>21.39607544</v>
-      </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+        <v>23.087</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.113873628321761</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -4070,13 +4117,13 @@
         <v>#N/A</v>
       </c>
       <c r="L27" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="M27" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="N27" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="O27" t="e">
         <v>#N/A</v>
@@ -4085,19 +4132,19 @@
         <v>248</v>
       </c>
       <c r="Q27" t="n">
-        <v>17.1684652566843</v>
+        <v>16.7765007746754</v>
       </c>
       <c r="R27" t="n">
-        <v>0.251175708814187</v>
+        <v>0.324548812636135</v>
       </c>
       <c r="S27" t="n">
-        <v>4.89363874858399</v>
+        <v>3.24197726155879</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
       </c>
       <c r="U27" s="9" t="n">
-        <v>31.10124</v>
+        <v>26.4838779963857</v>
       </c>
       <c r="V27" t="n">
         <v>3</v>
@@ -4109,17 +4156,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y27" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4129,16 +4176,16 @@
         <v>244</v>
       </c>
       <c r="F28" t="n">
-        <v>10.1</v>
+        <v>3.71</v>
       </c>
       <c r="G28" t="n">
-        <v>162.87</v>
+        <v>-42.9</v>
       </c>
       <c r="H28" t="n">
-        <v>21.83969502</v>
-      </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+        <v>23.094</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.11390636617795</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -4147,13 +4194,13 @@
         <v>#N/A</v>
       </c>
       <c r="L28" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="M28" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="N28" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="O28" t="e">
         <v>#N/A</v>
@@ -4162,19 +4209,19 @@
         <v>248</v>
       </c>
       <c r="Q28" t="n">
-        <v>16.8624417057763</v>
+        <v>16.9693759034212</v>
       </c>
       <c r="R28" t="n">
-        <v>0.369661960454139</v>
+        <v>0.275046287124662</v>
       </c>
       <c r="S28" t="n">
-        <v>4.04730679341278</v>
+        <v>3.22808215867071</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
       </c>
       <c r="U28" s="9" t="n">
-        <v>29.02104</v>
+        <v>26.4369510168393</v>
       </c>
       <c r="V28" t="n">
         <v>3</v>
@@ -4190,58 +4237,1390 @@
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="U29" s="9"/>
+      <c r="A29" t="s">
+        <v>274</v>
+      </c>
+      <c r="B29" t="s">
+        <v>241</v>
+      </c>
+      <c r="C29" t="s">
+        <v>242</v>
+      </c>
+      <c r="D29" t="s">
+        <v>243</v>
+      </c>
+      <c r="E29" t="s">
+        <v>244</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>23.157</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.11420098377263</v>
+      </c>
+      <c r="J29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L29" t="s">
+        <v>245</v>
+      </c>
+      <c r="M29" t="s">
+        <v>246</v>
+      </c>
+      <c r="N29" t="s">
+        <v>247</v>
+      </c>
+      <c r="O29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P29" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>17.3827020495579</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.284326395943221</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.81683320308599</v>
+      </c>
+      <c r="T29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U29" s="9" t="n">
+        <v>28.3054779254769</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3</v>
+      </c>
+      <c r="W29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="30" ht="19" customHeight="1">
-      <c r="U30" s="9"/>
+      <c r="A30" t="s">
+        <v>275</v>
+      </c>
+      <c r="B30" t="s">
+        <v>241</v>
+      </c>
+      <c r="C30" t="s">
+        <v>242</v>
+      </c>
+      <c r="D30" t="s">
+        <v>243</v>
+      </c>
+      <c r="E30" t="s">
+        <v>244</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>23.249</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.114631144442474</v>
+      </c>
+      <c r="J30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L30" t="s">
+        <v>245</v>
+      </c>
+      <c r="M30" t="s">
+        <v>246</v>
+      </c>
+      <c r="N30" t="s">
+        <v>247</v>
+      </c>
+      <c r="O30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P30" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>16.9598389490451</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.383080988680353</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.96904236109299</v>
+      </c>
+      <c r="T30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U30" s="9" t="n">
+        <v>28.7504364338809</v>
+      </c>
+      <c r="V30" t="n">
+        <v>3</v>
+      </c>
+      <c r="W30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="U31" s="9"/>
+      <c r="A31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B31" t="s">
+        <v>241</v>
+      </c>
+      <c r="C31" t="s">
+        <v>242</v>
+      </c>
+      <c r="D31" t="s">
+        <v>243</v>
+      </c>
+      <c r="E31" t="s">
+        <v>244</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>23.264</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.11470127096529</v>
+      </c>
+      <c r="J31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L31" t="s">
+        <v>245</v>
+      </c>
+      <c r="M31" t="s">
+        <v>246</v>
+      </c>
+      <c r="N31" t="s">
+        <v>247</v>
+      </c>
+      <c r="O31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P31" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>17.0005432749345</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.265259892381177</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.9061783735015</v>
+      </c>
+      <c r="T31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>28.5748192664753</v>
+      </c>
+      <c r="V31" t="n">
+        <v>3</v>
+      </c>
+      <c r="W31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="32" ht="19" customHeight="1">
-      <c r="U32" s="9"/>
+      <c r="A32" t="s">
+        <v>277</v>
+      </c>
+      <c r="B32" t="s">
+        <v>241</v>
+      </c>
+      <c r="C32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E32" t="s">
+        <v>244</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23.306</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.114897612774089</v>
+      </c>
+      <c r="J32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L32" t="s">
+        <v>245</v>
+      </c>
+      <c r="M32" t="s">
+        <v>246</v>
+      </c>
+      <c r="N32" t="s">
+        <v>247</v>
+      </c>
+      <c r="O32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P32" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>17.4301581886708</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.346992272933503</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.72015267324468</v>
+      </c>
+      <c r="T32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>28.0373604554315</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3</v>
+      </c>
+      <c r="W32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="33" ht="19" customHeight="1">
-      <c r="U33" s="9"/>
+      <c r="A33" t="s">
+        <v>278</v>
+      </c>
+      <c r="B33" t="s">
+        <v>241</v>
+      </c>
+      <c r="C33" t="s">
+        <v>242</v>
+      </c>
+      <c r="D33" t="s">
+        <v>243</v>
+      </c>
+      <c r="E33" t="s">
+        <v>244</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>23.338</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.11504719422985</v>
+      </c>
+      <c r="J33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L33" t="s">
+        <v>245</v>
+      </c>
+      <c r="M33" t="s">
+        <v>246</v>
+      </c>
+      <c r="N33" t="s">
+        <v>247</v>
+      </c>
+      <c r="O33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P33" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>17.284043435161</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.255476585754024</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.53284314304036</v>
+      </c>
+      <c r="T33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v>27.4669752408487</v>
+      </c>
+      <c r="V33" t="n">
+        <v>3</v>
+      </c>
+      <c r="W33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="34" ht="19" customHeight="1">
-      <c r="U34" s="9"/>
+      <c r="A34" t="s">
+        <v>279</v>
+      </c>
+      <c r="B34" t="s">
+        <v>241</v>
+      </c>
+      <c r="C34" t="s">
+        <v>242</v>
+      </c>
+      <c r="D34" t="s">
+        <v>243</v>
+      </c>
+      <c r="E34" t="s">
+        <v>244</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>23.575</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.116154702188319</v>
+      </c>
+      <c r="J34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L34" t="s">
+        <v>245</v>
+      </c>
+      <c r="M34" t="s">
+        <v>246</v>
+      </c>
+      <c r="N34" t="s">
+        <v>247</v>
+      </c>
+      <c r="O34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P34" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>17.2891799570572</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.247487231072573</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.44313706195881</v>
+      </c>
+      <c r="T34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U34" s="9" t="n">
+        <v>27.2081634091954</v>
+      </c>
+      <c r="V34" t="n">
+        <v>3</v>
+      </c>
+      <c r="W34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="U35" s="9"/>
+      <c r="A35" t="s">
+        <v>280</v>
+      </c>
+      <c r="B35" t="s">
+        <v>241</v>
+      </c>
+      <c r="C35" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" t="s">
+        <v>243</v>
+      </c>
+      <c r="E35" t="s">
+        <v>244</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>23.579</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.116173389340751</v>
+      </c>
+      <c r="J35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L35" t="s">
+        <v>245</v>
+      </c>
+      <c r="M35" t="s">
+        <v>246</v>
+      </c>
+      <c r="N35" t="s">
+        <v>247</v>
+      </c>
+      <c r="O35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P35" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>17.4164517289871</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.255708427674205</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.61510220513238</v>
+      </c>
+      <c r="T35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>27.7500904409772</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3</v>
+      </c>
+      <c r="W35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="U36" s="9"/>
+      <c r="A36" t="s">
+        <v>281</v>
+      </c>
+      <c r="B36" t="s">
+        <v>241</v>
+      </c>
+      <c r="C36" t="s">
+        <v>242</v>
+      </c>
+      <c r="D36" t="s">
+        <v>243</v>
+      </c>
+      <c r="E36" t="s">
+        <v>244</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23.662</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.116561110741634</v>
+      </c>
+      <c r="J36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L36" t="s">
+        <v>245</v>
+      </c>
+      <c r="M36" t="s">
+        <v>246</v>
+      </c>
+      <c r="N36" t="s">
+        <v>247</v>
+      </c>
+      <c r="O36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P36" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>17.570001141271</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.259190321713135</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.10510038895057</v>
+      </c>
+      <c r="T36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v>29.1719000256787</v>
+      </c>
+      <c r="V36" t="n">
+        <v>3</v>
+      </c>
+      <c r="W36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="37" ht="19" customHeight="1">
-      <c r="U37" s="9"/>
+      <c r="A37" t="s">
+        <v>282</v>
+      </c>
+      <c r="B37" t="s">
+        <v>241</v>
+      </c>
+      <c r="C37" t="s">
+        <v>242</v>
+      </c>
+      <c r="D37" t="s">
+        <v>243</v>
+      </c>
+      <c r="E37" t="s">
+        <v>244</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>23.733</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.116892720124033</v>
+      </c>
+      <c r="J37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L37" t="s">
+        <v>245</v>
+      </c>
+      <c r="M37" t="s">
+        <v>246</v>
+      </c>
+      <c r="N37" t="s">
+        <v>247</v>
+      </c>
+      <c r="O37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P37" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>16.8856857823266</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.257598634775819</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.74880508015526</v>
+      </c>
+      <c r="T37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U37" s="9" t="n">
+        <v>28.1711615795986</v>
+      </c>
+      <c r="V37" t="n">
+        <v>3</v>
+      </c>
+      <c r="W37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="38" ht="19" customHeight="1">
-      <c r="U38" s="9"/>
+      <c r="A38" t="s">
+        <v>283</v>
+      </c>
+      <c r="B38" t="s">
+        <v>241</v>
+      </c>
+      <c r="C38" t="s">
+        <v>242</v>
+      </c>
+      <c r="D38" t="s">
+        <v>243</v>
+      </c>
+      <c r="E38" t="s">
+        <v>244</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H38" t="n">
+        <v>23.797</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.11719159158428</v>
+      </c>
+      <c r="J38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L38" t="s">
+        <v>245</v>
+      </c>
+      <c r="M38" t="s">
+        <v>246</v>
+      </c>
+      <c r="N38" t="s">
+        <v>247</v>
+      </c>
+      <c r="O38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P38" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>17.24703499475</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.468031565685002</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.51107710944492</v>
+      </c>
+      <c r="T38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>27.4504980186116</v>
+      </c>
+      <c r="V38" t="n">
+        <v>3</v>
+      </c>
+      <c r="W38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="39" ht="19" customHeight="1">
-      <c r="U39" s="9"/>
+      <c r="A39" t="s">
+        <v>284</v>
+      </c>
+      <c r="B39" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" t="s">
+        <v>244</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H39" t="n">
+        <v>23.821</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.11730365764193</v>
+      </c>
+      <c r="J39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L39" t="s">
+        <v>245</v>
+      </c>
+      <c r="M39" t="s">
+        <v>246</v>
+      </c>
+      <c r="N39" t="s">
+        <v>247</v>
+      </c>
+      <c r="O39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P39" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>17.3065423193112</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.326321029229801</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.76517484704623</v>
+      </c>
+      <c r="T39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>28.2295294401807</v>
+      </c>
+      <c r="V39" t="n">
+        <v>3</v>
+      </c>
+      <c r="W39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="40" ht="19" customHeight="1">
-      <c r="U40" s="9"/>
+      <c r="A40" t="s">
+        <v>285</v>
+      </c>
+      <c r="B40" t="s">
+        <v>241</v>
+      </c>
+      <c r="C40" t="s">
+        <v>242</v>
+      </c>
+      <c r="D40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" t="s">
+        <v>244</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>23.857</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.11747174576442</v>
+      </c>
+      <c r="J40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L40" t="s">
+        <v>245</v>
+      </c>
+      <c r="M40" t="s">
+        <v>246</v>
+      </c>
+      <c r="N40" t="s">
+        <v>247</v>
+      </c>
+      <c r="O40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P40" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>16.2291334271057</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.851723329036432</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.03069909189815</v>
+      </c>
+      <c r="T40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U40" s="9" t="n">
+        <v>25.8225595036279</v>
+      </c>
+      <c r="V40" t="n">
+        <v>3</v>
+      </c>
+      <c r="W40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="41" ht="19" customHeight="1">
-      <c r="U41" s="9"/>
+      <c r="A41" t="s">
+        <v>286</v>
+      </c>
+      <c r="B41" t="s">
+        <v>241</v>
+      </c>
+      <c r="C41" t="s">
+        <v>242</v>
+      </c>
+      <c r="D41" t="s">
+        <v>243</v>
+      </c>
+      <c r="E41" t="s">
+        <v>244</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H41" t="n">
+        <v>23.928</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.117803214407298</v>
+      </c>
+      <c r="J41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L41" t="s">
+        <v>245</v>
+      </c>
+      <c r="M41" t="s">
+        <v>246</v>
+      </c>
+      <c r="N41" t="s">
+        <v>247</v>
+      </c>
+      <c r="O41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P41" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>17.4676979971724</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.278563195169932</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.57775891966691</v>
+      </c>
+      <c r="T41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>27.6744059393288</v>
+      </c>
+      <c r="V41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="42" ht="19" customHeight="1">
-      <c r="U42" s="9"/>
+      <c r="A42" t="s">
+        <v>287</v>
+      </c>
+      <c r="B42" t="s">
+        <v>241</v>
+      </c>
+      <c r="C42" t="s">
+        <v>242</v>
+      </c>
+      <c r="D42" t="s">
+        <v>243</v>
+      </c>
+      <c r="E42" t="s">
+        <v>244</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>23.978</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.118036612449318</v>
+      </c>
+      <c r="J42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L42" t="s">
+        <v>245</v>
+      </c>
+      <c r="M42" t="s">
+        <v>246</v>
+      </c>
+      <c r="N42" t="s">
+        <v>247</v>
+      </c>
+      <c r="O42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P42" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>17.8274441435575</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.386703883810618</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.54111729902704</v>
+      </c>
+      <c r="T42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v>27.5657538847913</v>
+      </c>
+      <c r="V42" t="n">
+        <v>3</v>
+      </c>
+      <c r="W42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="43" ht="19" customHeight="1">
-      <c r="U43" s="9"/>
+      <c r="A43" t="s">
+        <v>288</v>
+      </c>
+      <c r="B43" t="s">
+        <v>241</v>
+      </c>
+      <c r="C43" t="s">
+        <v>242</v>
+      </c>
+      <c r="D43" t="s">
+        <v>243</v>
+      </c>
+      <c r="E43" t="s">
+        <v>244</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="H43" t="n">
+        <v>24.018</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.118223312729582</v>
+      </c>
+      <c r="J43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L43" t="s">
+        <v>245</v>
+      </c>
+      <c r="M43" t="s">
+        <v>246</v>
+      </c>
+      <c r="N43" t="s">
+        <v>247</v>
+      </c>
+      <c r="O43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P43" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>17.3084676647876</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.686913523088993</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.93656502226994</v>
+      </c>
+      <c r="T43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U43" s="9" t="n">
+        <v>28.7465015506555</v>
+      </c>
+      <c r="V43" t="n">
+        <v>3</v>
+      </c>
+      <c r="W43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="44" ht="19" customHeight="1">
-      <c r="U44" s="9"/>
+      <c r="A44" t="s">
+        <v>289</v>
+      </c>
+      <c r="B44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" t="s">
+        <v>242</v>
+      </c>
+      <c r="D44" t="s">
+        <v>243</v>
+      </c>
+      <c r="E44" t="s">
+        <v>244</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>162.87</v>
+      </c>
+      <c r="H44" t="n">
+        <v>21.16732075</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.104875607610009</v>
+      </c>
+      <c r="J44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L44" t="s">
+        <v>290</v>
+      </c>
+      <c r="M44" t="s">
+        <v>291</v>
+      </c>
+      <c r="N44" t="s">
+        <v>292</v>
+      </c>
+      <c r="O44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P44" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>16.6553386622114</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.248765002131439</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4.4524375655714</v>
+      </c>
+      <c r="T44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U44" s="9" t="n">
+        <v>29.92866</v>
+      </c>
+      <c r="V44" t="n">
+        <v>3</v>
+      </c>
+      <c r="W44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="45" ht="19" customHeight="1">
-      <c r="U45" s="9"/>
+      <c r="A45" t="s">
+        <v>293</v>
+      </c>
+      <c r="B45" t="s">
+        <v>241</v>
+      </c>
+      <c r="C45" t="s">
+        <v>242</v>
+      </c>
+      <c r="D45" t="s">
+        <v>243</v>
+      </c>
+      <c r="E45" t="s">
+        <v>244</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>162.87</v>
+      </c>
+      <c r="H45" t="n">
+        <v>21.39607544</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.105949986431882</v>
+      </c>
+      <c r="J45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L45" t="s">
+        <v>290</v>
+      </c>
+      <c r="M45" t="s">
+        <v>291</v>
+      </c>
+      <c r="N45" t="s">
+        <v>292</v>
+      </c>
+      <c r="O45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P45" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>17.1684652566843</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.251175708814187</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4.89363874858399</v>
+      </c>
+      <c r="T45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U45" s="9" t="n">
+        <v>31.10124</v>
+      </c>
+      <c r="V45" t="n">
+        <v>3</v>
+      </c>
+      <c r="W45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="46" ht="19" customHeight="1">
-      <c r="U46" s="9"/>
+      <c r="A46" t="s">
+        <v>294</v>
+      </c>
+      <c r="B46" t="s">
+        <v>241</v>
+      </c>
+      <c r="C46" t="s">
+        <v>242</v>
+      </c>
+      <c r="D46" t="s">
+        <v>243</v>
+      </c>
+      <c r="E46" t="s">
+        <v>244</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>162.87</v>
+      </c>
+      <c r="H46" t="n">
+        <v>21.83969502</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.108031819203302</v>
+      </c>
+      <c r="J46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L46" t="s">
+        <v>290</v>
+      </c>
+      <c r="M46" t="s">
+        <v>291</v>
+      </c>
+      <c r="N46" t="s">
+        <v>292</v>
+      </c>
+      <c r="O46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P46" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>16.8624417057763</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.369661960454139</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4.04730679341278</v>
+      </c>
+      <c r="T46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U46" s="9" t="n">
+        <v>29.02104</v>
+      </c>
+      <c r="V46" t="n">
+        <v>3</v>
+      </c>
+      <c r="W46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="U47" s="9"/>
@@ -4429,32 +5808,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
